--- a/doc-school/ws5/BShoes_DefectReport.xlsx
+++ b/doc-school/ws5/BShoes_DefectReport.xlsx
@@ -129,7 +129,7 @@
     <t>Related Testcase ID</t>
   </si>
   <si>
-    <t>Module: Đăng nhập (Sprint 3 - TEST)</t>
+    <t>Module: Đăng nhập — pb-1 / Sprint 1 / RQ-1  (phát hiện ở Sprint 3 - TEST)</t>
   </si>
   <si>
     <t>BUG_DN_01</t>
@@ -164,7 +164,7 @@
     <t>DN_13</t>
   </si>
   <si>
-    <t>Module: Quản lý nhân viên (Sprint 3 - TEST)</t>
+    <t>Module: Quản lý nhân viên — pb-2 / Sprint 1 / RQ-2,RQ-3,RQ-4  (phát hiện ở Sprint 3 - TEST)</t>
   </si>
   <si>
     <t>BUG_NV_01</t>
@@ -196,7 +196,7 @@
     <t>NV_08</t>
   </si>
   <si>
-    <t>Module: Quản lý sản phẩm (Sprint 3 - TEST)</t>
+    <t>Module: Quản lý sản phẩm — pb-3 / Sprint 1 / RQ-5,RQ-6,RQ-9  (phát hiện ở Sprint 3 - TEST)</t>
   </si>
   <si>
     <t>BUG_SP_01</t>
@@ -239,7 +239,7 @@
     <t>SP_13</t>
   </si>
   <si>
-    <t>Module: Bán hàng - POS (Sprint 3 - TEST)</t>
+    <t>Module: Bán hàng POS — PB-5 / Sprint 2 / RQ-11→RQ-18  (phát hiện ở Sprint 3 - TEST)</t>
   </si>
   <si>
     <t>BUG_POS_01</t>
@@ -284,7 +284,7 @@
     <t>POS_19</t>
   </si>
   <si>
-    <t>Module: Quản lý phiếu giảm giá (Sprint 3 - TEST)</t>
+    <t>Module: Quản lý phiếu giảm giá — PB-6 / Sprint 2 / RQ-21  (phát hiện ở Sprint 3 - TEST)</t>
   </si>
   <si>
     <t>BUG_PGG_01</t>
@@ -304,7 +304,7 @@
     <t>PGG_05</t>
   </si>
   <si>
-    <t>Module: Quản lý trả hàng (Sprint 3 - TEST)</t>
+    <t>Module: Quản lý trả hàng — PB-7 / Sprint 3 / RQ-22  (phát hiện ở Sprint 3 - TEST)</t>
   </si>
   <si>
     <t>BUG_TH_01</t>
